--- a/templates/23-kano-analysis.xlsx
+++ b/templates/23-kano-analysis.xlsx
@@ -825,109 +825,193 @@
         </is>
       </c>
       <c r="D7" s="8">
-        <f>IF(OR(B7="",C7=""),"",IF(AND(B7="Like",C7="Dislike"),"Delighter",IF(AND(B7="Like",OR(C7="Live with it",C7="Neutral")),"Delighter",IF(AND(B7="Expect it",C7="Dislike"),"Performance",IF(C7="Dislike","Must-have",IF(AND(B7="Neutral",C7="Neutral"),"Indifferent","Indifferent"))))))</f>
+        <f>IF(OR(B7="",C7=""),"",IF(B7="Like",IF(C7="Like","Questionable",IF(C7="Dislike","Performance","Delighter")),IF(B7="Dislike",IF(C7="Dislike","Questionable","Reverse"),IF(C7="Dislike","Must-have",IF(C7="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
       <c r="E7" s="8">
-        <f>IF(D7="","",IF(D7="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D7="Performance","Invest — more is better, and measurable",IF(D7="Delighter","Consider — wins goodwill, does not lose you anything if absent","Do not spend here"))))</f>
+        <f>IF(D7="","",IF(D7="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D7="Performance","Invest — more is better, and measurable",IF(D7="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D7="Reverse","Stop doing it — they want the opposite",IF(D7="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
       <c r="F7" s="7" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="n"/>
-      <c r="B8" s="9" t="n"/>
-      <c r="C8" s="9" t="n"/>
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Answered within the time you promised</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Expect it</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Dislike</t>
+        </is>
+      </c>
       <c r="D8" s="10">
-        <f>IF(OR(B8="",C8=""),"",IF(AND(B8="Like",C8="Dislike"),"Delighter",IF(AND(B8="Like",OR(C8="Live with it",C8="Neutral")),"Delighter",IF(AND(B8="Expect it",C8="Dislike"),"Performance",IF(C8="Dislike","Must-have",IF(AND(B8="Neutral",C8="Neutral"),"Indifferent","Indifferent"))))))</f>
+        <f>IF(OR(B8="",C8=""),"",IF(B8="Like",IF(C8="Like","Questionable",IF(C8="Dislike","Performance","Delighter")),IF(B8="Dislike",IF(C8="Dislike","Questionable","Reverse"),IF(C8="Dislike","Must-have",IF(C8="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
       <c r="E8" s="10">
-        <f>IF(D8="","",IF(D8="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D8="Performance","Invest — more is better, and measurable",IF(D8="Delighter","Consider — wins goodwill, does not lose you anything if absent","Do not spend here"))))</f>
+        <f>IF(D8="","",IF(D8="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D8="Performance","Invest — more is better, and measurable",IF(D8="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D8="Reverse","Stop doing it — they want the opposite",IF(D8="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
       <c r="F8" s="9" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="n"/>
-      <c r="B9" s="9" t="n"/>
-      <c r="C9" s="9" t="n"/>
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Agent already knows my account history</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Like</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Dislike</t>
+        </is>
+      </c>
       <c r="D9" s="10">
-        <f>IF(OR(B9="",C9=""),"",IF(AND(B9="Like",C9="Dislike"),"Delighter",IF(AND(B9="Like",OR(C9="Live with it",C9="Neutral")),"Delighter",IF(AND(B9="Expect it",C9="Dislike"),"Performance",IF(C9="Dislike","Must-have",IF(AND(B9="Neutral",C9="Neutral"),"Indifferent","Indifferent"))))))</f>
+        <f>IF(OR(B9="",C9=""),"",IF(B9="Like",IF(C9="Like","Questionable",IF(C9="Dislike","Performance","Delighter")),IF(B9="Dislike",IF(C9="Dislike","Questionable","Reverse"),IF(C9="Dislike","Must-have",IF(C9="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
       <c r="E9" s="10">
-        <f>IF(D9="","",IF(D9="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D9="Performance","Invest — more is better, and measurable",IF(D9="Delighter","Consider — wins goodwill, does not lose you anything if absent","Do not spend here"))))</f>
+        <f>IF(D9="","",IF(D9="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D9="Performance","Invest — more is better, and measurable",IF(D9="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D9="Reverse","Stop doing it — they want the opposite",IF(D9="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
       <c r="F9" s="9" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="n"/>
-      <c r="B10" s="9" t="n"/>
-      <c r="C10" s="9" t="n"/>
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Fewer transfers between teams</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Like</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Dislike</t>
+        </is>
+      </c>
       <c r="D10" s="10">
-        <f>IF(OR(B10="",C10=""),"",IF(AND(B10="Like",C10="Dislike"),"Delighter",IF(AND(B10="Like",OR(C10="Live with it",C10="Neutral")),"Delighter",IF(AND(B10="Expect it",C10="Dislike"),"Performance",IF(C10="Dislike","Must-have",IF(AND(B10="Neutral",C10="Neutral"),"Indifferent","Indifferent"))))))</f>
+        <f>IF(OR(B10="",C10=""),"",IF(B10="Like",IF(C10="Like","Questionable",IF(C10="Dislike","Performance","Delighter")),IF(B10="Dislike",IF(C10="Dislike","Questionable","Reverse"),IF(C10="Dislike","Must-have",IF(C10="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
       <c r="E10" s="10">
-        <f>IF(D10="","",IF(D10="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D10="Performance","Invest — more is better, and measurable",IF(D10="Delighter","Consider — wins goodwill, does not lose you anything if absent","Do not spend here"))))</f>
+        <f>IF(D10="","",IF(D10="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D10="Performance","Invest — more is better, and measurable",IF(D10="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D10="Reverse","Stop doing it — they want the opposite",IF(D10="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
       <c r="F10" s="9" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="n"/>
-      <c r="B11" s="9" t="n"/>
-      <c r="C11" s="9" t="n"/>
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Proactive notice before I notice the problem</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Like</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Live with it</t>
+        </is>
+      </c>
       <c r="D11" s="10">
-        <f>IF(OR(B11="",C11=""),"",IF(AND(B11="Like",C11="Dislike"),"Delighter",IF(AND(B11="Like",OR(C11="Live with it",C11="Neutral")),"Delighter",IF(AND(B11="Expect it",C11="Dislike"),"Performance",IF(C11="Dislike","Must-have",IF(AND(B11="Neutral",C11="Neutral"),"Indifferent","Indifferent"))))))</f>
+        <f>IF(OR(B11="",C11=""),"",IF(B11="Like",IF(C11="Like","Questionable",IF(C11="Dislike","Performance","Delighter")),IF(B11="Dislike",IF(C11="Dislike","Questionable","Reverse"),IF(C11="Dislike","Must-have",IF(C11="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
       <c r="E11" s="10">
-        <f>IF(D11="","",IF(D11="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D11="Performance","Invest — more is better, and measurable",IF(D11="Delighter","Consider — wins goodwill, does not lose you anything if absent","Do not spend here"))))</f>
+        <f>IF(D11="","",IF(D11="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D11="Performance","Invest — more is better, and measurable",IF(D11="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D11="Reverse","Stop doing it — they want the opposite",IF(D11="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
       <c r="F11" s="9" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="n"/>
-      <c r="B12" s="9" t="n"/>
-      <c r="C12" s="9" t="n"/>
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>A follow-up note a week later</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Like</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
       <c r="D12" s="10">
-        <f>IF(OR(B12="",C12=""),"",IF(AND(B12="Like",C12="Dislike"),"Delighter",IF(AND(B12="Like",OR(C12="Live with it",C12="Neutral")),"Delighter",IF(AND(B12="Expect it",C12="Dislike"),"Performance",IF(C12="Dislike","Must-have",IF(AND(B12="Neutral",C12="Neutral"),"Indifferent","Indifferent"))))))</f>
+        <f>IF(OR(B12="",C12=""),"",IF(B12="Like",IF(C12="Like","Questionable",IF(C12="Dislike","Performance","Delighter")),IF(B12="Dislike",IF(C12="Dislike","Questionable","Reverse"),IF(C12="Dislike","Must-have",IF(C12="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
       <c r="E12" s="10">
-        <f>IF(D12="","",IF(D12="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D12="Performance","Invest — more is better, and measurable",IF(D12="Delighter","Consider — wins goodwill, does not lose you anything if absent","Do not spend here"))))</f>
+        <f>IF(D12="","",IF(D12="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D12="Performance","Invest — more is better, and measurable",IF(D12="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D12="Reverse","Stop doing it — they want the opposite",IF(D12="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
       <c r="F12" s="9" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="n"/>
-      <c r="B13" s="9" t="n"/>
-      <c r="C13" s="9" t="n"/>
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>Choice of chat colour scheme</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
       <c r="D13" s="10">
-        <f>IF(OR(B13="",C13=""),"",IF(AND(B13="Like",C13="Dislike"),"Delighter",IF(AND(B13="Like",OR(C13="Live with it",C13="Neutral")),"Delighter",IF(AND(B13="Expect it",C13="Dislike"),"Performance",IF(C13="Dislike","Must-have",IF(AND(B13="Neutral",C13="Neutral"),"Indifferent","Indifferent"))))))</f>
+        <f>IF(OR(B13="",C13=""),"",IF(B13="Like",IF(C13="Like","Questionable",IF(C13="Dislike","Performance","Delighter")),IF(B13="Dislike",IF(C13="Dislike","Questionable","Reverse"),IF(C13="Dislike","Must-have",IF(C13="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
       <c r="E13" s="10">
-        <f>IF(D13="","",IF(D13="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D13="Performance","Invest — more is better, and measurable",IF(D13="Delighter","Consider — wins goodwill, does not lose you anything if absent","Do not spend here"))))</f>
+        <f>IF(D13="","",IF(D13="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D13="Performance","Invest — more is better, and measurable",IF(D13="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D13="Reverse","Stop doing it — they want the opposite",IF(D13="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
       <c r="F13" s="9" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="n"/>
-      <c r="B14" s="9" t="n"/>
-      <c r="C14" s="9" t="n"/>
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>A survey after every single contact</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Dislike</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
       <c r="D14" s="10">
-        <f>IF(OR(B14="",C14=""),"",IF(AND(B14="Like",C14="Dislike"),"Delighter",IF(AND(B14="Like",OR(C14="Live with it",C14="Neutral")),"Delighter",IF(AND(B14="Expect it",C14="Dislike"),"Performance",IF(C14="Dislike","Must-have",IF(AND(B14="Neutral",C14="Neutral"),"Indifferent","Indifferent"))))))</f>
+        <f>IF(OR(B14="",C14=""),"",IF(B14="Like",IF(C14="Like","Questionable",IF(C14="Dislike","Performance","Delighter")),IF(B14="Dislike",IF(C14="Dislike","Questionable","Reverse"),IF(C14="Dislike","Must-have",IF(C14="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
       <c r="E14" s="10">
-        <f>IF(D14="","",IF(D14="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D14="Performance","Invest — more is better, and measurable",IF(D14="Delighter","Consider — wins goodwill, does not lose you anything if absent","Do not spend here"))))</f>
+        <f>IF(D14="","",IF(D14="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D14="Performance","Invest — more is better, and measurable",IF(D14="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D14="Reverse","Stop doing it — they want the opposite",IF(D14="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
       <c r="F14" s="9" t="n"/>
@@ -937,11 +1021,11 @@
       <c r="B15" s="9" t="n"/>
       <c r="C15" s="9" t="n"/>
       <c r="D15" s="10">
-        <f>IF(OR(B15="",C15=""),"",IF(AND(B15="Like",C15="Dislike"),"Delighter",IF(AND(B15="Like",OR(C15="Live with it",C15="Neutral")),"Delighter",IF(AND(B15="Expect it",C15="Dislike"),"Performance",IF(C15="Dislike","Must-have",IF(AND(B15="Neutral",C15="Neutral"),"Indifferent","Indifferent"))))))</f>
+        <f>IF(OR(B15="",C15=""),"",IF(B15="Like",IF(C15="Like","Questionable",IF(C15="Dislike","Performance","Delighter")),IF(B15="Dislike",IF(C15="Dislike","Questionable","Reverse"),IF(C15="Dislike","Must-have",IF(C15="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
       <c r="E15" s="10">
-        <f>IF(D15="","",IF(D15="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D15="Performance","Invest — more is better, and measurable",IF(D15="Delighter","Consider — wins goodwill, does not lose you anything if absent","Do not spend here"))))</f>
+        <f>IF(D15="","",IF(D15="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D15="Performance","Invest — more is better, and measurable",IF(D15="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D15="Reverse","Stop doing it — they want the opposite",IF(D15="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
       <c r="F15" s="9" t="n"/>
@@ -951,11 +1035,11 @@
       <c r="B16" s="9" t="n"/>
       <c r="C16" s="9" t="n"/>
       <c r="D16" s="10">
-        <f>IF(OR(B16="",C16=""),"",IF(AND(B16="Like",C16="Dislike"),"Delighter",IF(AND(B16="Like",OR(C16="Live with it",C16="Neutral")),"Delighter",IF(AND(B16="Expect it",C16="Dislike"),"Performance",IF(C16="Dislike","Must-have",IF(AND(B16="Neutral",C16="Neutral"),"Indifferent","Indifferent"))))))</f>
+        <f>IF(OR(B16="",C16=""),"",IF(B16="Like",IF(C16="Like","Questionable",IF(C16="Dislike","Performance","Delighter")),IF(B16="Dislike",IF(C16="Dislike","Questionable","Reverse"),IF(C16="Dislike","Must-have",IF(C16="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
       <c r="E16" s="10">
-        <f>IF(D16="","",IF(D16="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D16="Performance","Invest — more is better, and measurable",IF(D16="Delighter","Consider — wins goodwill, does not lose you anything if absent","Do not spend here"))))</f>
+        <f>IF(D16="","",IF(D16="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D16="Performance","Invest — more is better, and measurable",IF(D16="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D16="Reverse","Stop doing it — they want the opposite",IF(D16="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
       <c r="F16" s="9" t="n"/>
@@ -965,11 +1049,11 @@
       <c r="B17" s="9" t="n"/>
       <c r="C17" s="9" t="n"/>
       <c r="D17" s="10">
-        <f>IF(OR(B17="",C17=""),"",IF(AND(B17="Like",C17="Dislike"),"Delighter",IF(AND(B17="Like",OR(C17="Live with it",C17="Neutral")),"Delighter",IF(AND(B17="Expect it",C17="Dislike"),"Performance",IF(C17="Dislike","Must-have",IF(AND(B17="Neutral",C17="Neutral"),"Indifferent","Indifferent"))))))</f>
+        <f>IF(OR(B17="",C17=""),"",IF(B17="Like",IF(C17="Like","Questionable",IF(C17="Dislike","Performance","Delighter")),IF(B17="Dislike",IF(C17="Dislike","Questionable","Reverse"),IF(C17="Dislike","Must-have",IF(C17="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
       <c r="E17" s="10">
-        <f>IF(D17="","",IF(D17="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D17="Performance","Invest — more is better, and measurable",IF(D17="Delighter","Consider — wins goodwill, does not lose you anything if absent","Do not spend here"))))</f>
+        <f>IF(D17="","",IF(D17="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D17="Performance","Invest — more is better, and measurable",IF(D17="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D17="Reverse","Stop doing it — they want the opposite",IF(D17="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
       <c r="F17" s="9" t="n"/>
@@ -979,11 +1063,11 @@
       <c r="B18" s="9" t="n"/>
       <c r="C18" s="9" t="n"/>
       <c r="D18" s="10">
-        <f>IF(OR(B18="",C18=""),"",IF(AND(B18="Like",C18="Dislike"),"Delighter",IF(AND(B18="Like",OR(C18="Live with it",C18="Neutral")),"Delighter",IF(AND(B18="Expect it",C18="Dislike"),"Performance",IF(C18="Dislike","Must-have",IF(AND(B18="Neutral",C18="Neutral"),"Indifferent","Indifferent"))))))</f>
+        <f>IF(OR(B18="",C18=""),"",IF(B18="Like",IF(C18="Like","Questionable",IF(C18="Dislike","Performance","Delighter")),IF(B18="Dislike",IF(C18="Dislike","Questionable","Reverse"),IF(C18="Dislike","Must-have",IF(C18="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
       <c r="E18" s="10">
-        <f>IF(D18="","",IF(D18="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D18="Performance","Invest — more is better, and measurable",IF(D18="Delighter","Consider — wins goodwill, does not lose you anything if absent","Do not spend here"))))</f>
+        <f>IF(D18="","",IF(D18="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D18="Performance","Invest — more is better, and measurable",IF(D18="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D18="Reverse","Stop doing it — they want the opposite",IF(D18="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
       <c r="F18" s="9" t="n"/>
@@ -993,11 +1077,11 @@
       <c r="B19" s="9" t="n"/>
       <c r="C19" s="9" t="n"/>
       <c r="D19" s="10">
-        <f>IF(OR(B19="",C19=""),"",IF(AND(B19="Like",C19="Dislike"),"Delighter",IF(AND(B19="Like",OR(C19="Live with it",C19="Neutral")),"Delighter",IF(AND(B19="Expect it",C19="Dislike"),"Performance",IF(C19="Dislike","Must-have",IF(AND(B19="Neutral",C19="Neutral"),"Indifferent","Indifferent"))))))</f>
+        <f>IF(OR(B19="",C19=""),"",IF(B19="Like",IF(C19="Like","Questionable",IF(C19="Dislike","Performance","Delighter")),IF(B19="Dislike",IF(C19="Dislike","Questionable","Reverse"),IF(C19="Dislike","Must-have",IF(C19="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
       <c r="E19" s="10">
-        <f>IF(D19="","",IF(D19="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D19="Performance","Invest — more is better, and measurable",IF(D19="Delighter","Consider — wins goodwill, does not lose you anything if absent","Do not spend here"))))</f>
+        <f>IF(D19="","",IF(D19="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D19="Performance","Invest — more is better, and measurable",IF(D19="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D19="Reverse","Stop doing it — they want the opposite",IF(D19="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
       <c r="F19" s="9" t="n"/>
@@ -1007,11 +1091,11 @@
       <c r="B20" s="9" t="n"/>
       <c r="C20" s="9" t="n"/>
       <c r="D20" s="10">
-        <f>IF(OR(B20="",C20=""),"",IF(AND(B20="Like",C20="Dislike"),"Delighter",IF(AND(B20="Like",OR(C20="Live with it",C20="Neutral")),"Delighter",IF(AND(B20="Expect it",C20="Dislike"),"Performance",IF(C20="Dislike","Must-have",IF(AND(B20="Neutral",C20="Neutral"),"Indifferent","Indifferent"))))))</f>
+        <f>IF(OR(B20="",C20=""),"",IF(B20="Like",IF(C20="Like","Questionable",IF(C20="Dislike","Performance","Delighter")),IF(B20="Dislike",IF(C20="Dislike","Questionable","Reverse"),IF(C20="Dislike","Must-have",IF(C20="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
       <c r="E20" s="10">
-        <f>IF(D20="","",IF(D20="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D20="Performance","Invest — more is better, and measurable",IF(D20="Delighter","Consider — wins goodwill, does not lose you anything if absent","Do not spend here"))))</f>
+        <f>IF(D20="","",IF(D20="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D20="Performance","Invest — more is better, and measurable",IF(D20="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D20="Reverse","Stop doing it — they want the opposite",IF(D20="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
       <c r="F20" s="9" t="n"/>
@@ -1021,11 +1105,11 @@
       <c r="B21" s="9" t="n"/>
       <c r="C21" s="9" t="n"/>
       <c r="D21" s="10">
-        <f>IF(OR(B21="",C21=""),"",IF(AND(B21="Like",C21="Dislike"),"Delighter",IF(AND(B21="Like",OR(C21="Live with it",C21="Neutral")),"Delighter",IF(AND(B21="Expect it",C21="Dislike"),"Performance",IF(C21="Dislike","Must-have",IF(AND(B21="Neutral",C21="Neutral"),"Indifferent","Indifferent"))))))</f>
+        <f>IF(OR(B21="",C21=""),"",IF(B21="Like",IF(C21="Like","Questionable",IF(C21="Dislike","Performance","Delighter")),IF(B21="Dislike",IF(C21="Dislike","Questionable","Reverse"),IF(C21="Dislike","Must-have",IF(C21="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
       <c r="E21" s="10">
-        <f>IF(D21="","",IF(D21="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D21="Performance","Invest — more is better, and measurable",IF(D21="Delighter","Consider — wins goodwill, does not lose you anything if absent","Do not spend here"))))</f>
+        <f>IF(D21="","",IF(D21="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D21="Performance","Invest — more is better, and measurable",IF(D21="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D21="Reverse","Stop doing it — they want the opposite",IF(D21="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
       <c r="F21" s="9" t="n"/>
@@ -1035,11 +1119,11 @@
       <c r="B22" s="9" t="n"/>
       <c r="C22" s="9" t="n"/>
       <c r="D22" s="10">
-        <f>IF(OR(B22="",C22=""),"",IF(AND(B22="Like",C22="Dislike"),"Delighter",IF(AND(B22="Like",OR(C22="Live with it",C22="Neutral")),"Delighter",IF(AND(B22="Expect it",C22="Dislike"),"Performance",IF(C22="Dislike","Must-have",IF(AND(B22="Neutral",C22="Neutral"),"Indifferent","Indifferent"))))))</f>
+        <f>IF(OR(B22="",C22=""),"",IF(B22="Like",IF(C22="Like","Questionable",IF(C22="Dislike","Performance","Delighter")),IF(B22="Dislike",IF(C22="Dislike","Questionable","Reverse"),IF(C22="Dislike","Must-have",IF(C22="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
       <c r="E22" s="10">
-        <f>IF(D22="","",IF(D22="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D22="Performance","Invest — more is better, and measurable",IF(D22="Delighter","Consider — wins goodwill, does not lose you anything if absent","Do not spend here"))))</f>
+        <f>IF(D22="","",IF(D22="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D22="Performance","Invest — more is better, and measurable",IF(D22="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D22="Reverse","Stop doing it — they want the opposite",IF(D22="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
       <c r="F22" s="9" t="n"/>
@@ -1049,11 +1133,11 @@
       <c r="B23" s="9" t="n"/>
       <c r="C23" s="9" t="n"/>
       <c r="D23" s="10">
-        <f>IF(OR(B23="",C23=""),"",IF(AND(B23="Like",C23="Dislike"),"Delighter",IF(AND(B23="Like",OR(C23="Live with it",C23="Neutral")),"Delighter",IF(AND(B23="Expect it",C23="Dislike"),"Performance",IF(C23="Dislike","Must-have",IF(AND(B23="Neutral",C23="Neutral"),"Indifferent","Indifferent"))))))</f>
+        <f>IF(OR(B23="",C23=""),"",IF(B23="Like",IF(C23="Like","Questionable",IF(C23="Dislike","Performance","Delighter")),IF(B23="Dislike",IF(C23="Dislike","Questionable","Reverse"),IF(C23="Dislike","Must-have",IF(C23="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
       <c r="E23" s="10">
-        <f>IF(D23="","",IF(D23="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D23="Performance","Invest — more is better, and measurable",IF(D23="Delighter","Consider — wins goodwill, does not lose you anything if absent","Do not spend here"))))</f>
+        <f>IF(D23="","",IF(D23="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D23="Performance","Invest — more is better, and measurable",IF(D23="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D23="Reverse","Stop doing it — they want the opposite",IF(D23="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
       <c r="F23" s="9" t="n"/>
@@ -1063,11 +1147,11 @@
       <c r="B24" s="9" t="n"/>
       <c r="C24" s="9" t="n"/>
       <c r="D24" s="10">
-        <f>IF(OR(B24="",C24=""),"",IF(AND(B24="Like",C24="Dislike"),"Delighter",IF(AND(B24="Like",OR(C24="Live with it",C24="Neutral")),"Delighter",IF(AND(B24="Expect it",C24="Dislike"),"Performance",IF(C24="Dislike","Must-have",IF(AND(B24="Neutral",C24="Neutral"),"Indifferent","Indifferent"))))))</f>
+        <f>IF(OR(B24="",C24=""),"",IF(B24="Like",IF(C24="Like","Questionable",IF(C24="Dislike","Performance","Delighter")),IF(B24="Dislike",IF(C24="Dislike","Questionable","Reverse"),IF(C24="Dislike","Must-have",IF(C24="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
       <c r="E24" s="10">
-        <f>IF(D24="","",IF(D24="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D24="Performance","Invest — more is better, and measurable",IF(D24="Delighter","Consider — wins goodwill, does not lose you anything if absent","Do not spend here"))))</f>
+        <f>IF(D24="","",IF(D24="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D24="Performance","Invest — more is better, and measurable",IF(D24="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D24="Reverse","Stop doing it — they want the opposite",IF(D24="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
       <c r="F24" s="9" t="n"/>
@@ -1077,11 +1161,11 @@
       <c r="B25" s="9" t="n"/>
       <c r="C25" s="9" t="n"/>
       <c r="D25" s="10">
-        <f>IF(OR(B25="",C25=""),"",IF(AND(B25="Like",C25="Dislike"),"Delighter",IF(AND(B25="Like",OR(C25="Live with it",C25="Neutral")),"Delighter",IF(AND(B25="Expect it",C25="Dislike"),"Performance",IF(C25="Dislike","Must-have",IF(AND(B25="Neutral",C25="Neutral"),"Indifferent","Indifferent"))))))</f>
+        <f>IF(OR(B25="",C25=""),"",IF(B25="Like",IF(C25="Like","Questionable",IF(C25="Dislike","Performance","Delighter")),IF(B25="Dislike",IF(C25="Dislike","Questionable","Reverse"),IF(C25="Dislike","Must-have",IF(C25="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
       <c r="E25" s="10">
-        <f>IF(D25="","",IF(D25="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D25="Performance","Invest — more is better, and measurable",IF(D25="Delighter","Consider — wins goodwill, does not lose you anything if absent","Do not spend here"))))</f>
+        <f>IF(D25="","",IF(D25="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D25="Performance","Invest — more is better, and measurable",IF(D25="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D25="Reverse","Stop doing it — they want the opposite",IF(D25="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
       <c r="F25" s="9" t="n"/>

--- a/templates/23-kano-analysis.xlsx
+++ b/templates/23-kano-analysis.xlsx
@@ -235,10 +235,17 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
+            <a:solidFill>
+              <a:srgbClr val="1F4E79"/>
+            </a:solidFill>
             <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="1F4E79"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'Kano analysis'!$A$28:$A$31</f>

--- a/templates/23-kano-analysis.xlsx
+++ b/templates/23-kano-analysis.xlsx
@@ -221,7 +221,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Where your requirements fall</a:t>
+              <a:t>Where your requirements fall — and which ones are worth money</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -235,17 +235,55 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:solidFill>
-              <a:srgbClr val="1F4E79"/>
-            </a:solidFill>
             <a:ln>
-              <a:solidFill>
-                <a:srgbClr val="1F4E79"/>
-              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <invertIfNegative val="0"/>
+          <dPt>
+            <idx val="0"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="C0392B"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="1F4E79"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="2"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="3F8F5A"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="3"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="9AA4B2"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
           <cat>
             <numRef>
               <f>'Kano analysis'!$A$28:$A$31</f>

--- a/templates/23-kano-analysis.xlsx
+++ b/templates/23-kano-analysis.xlsx
@@ -244,7 +244,7 @@
             <idx val="0"/>
             <spPr>
               <a:solidFill>
-                <a:srgbClr val="C0392B"/>
+                <a:srgbClr val="B45309"/>
               </a:solidFill>
               <a:ln>
                 <a:prstDash val="solid"/>
@@ -284,14 +284,36 @@
               </a:ln>
             </spPr>
           </dPt>
+          <dPt>
+            <idx val="4"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="C0392B"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="5"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="6B4FA0"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
           <cat>
             <numRef>
-              <f>'Kano analysis'!$A$28:$A$31</f>
+              <f>'Kano analysis'!$A$28:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Kano analysis'!$D$28:$D$31</f>
+              <f>'Kano analysis'!$D$28:$D$33</f>
             </numRef>
           </val>
         </ser>
@@ -782,7 +804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1271,23 +1293,47 @@
         <v/>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>Reverse — you are actively annoying people</t>
+        </is>
+      </c>
+      <c r="D32" s="10">
+        <f>COUNTIF($D$7:$D$25,"Reverse")</f>
+        <v/>
+      </c>
+    </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>Questionable — the answers contradict; re-ask</t>
+        </is>
+      </c>
+      <c r="D33" s="10">
+        <f>COUNTIF($D$7:$D$25,"Questionable")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>Speed in support is usually a must-have: being twice as fast wins you nothing once you are fast enough, while being slow loses you everything. Spending your improvement budget on a must-have that is already met is the most common way to move a metric and change nothing.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="11">
     <mergeCell ref="A28:C28"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A32:C32"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A31:C31"/>
     <mergeCell ref="A27:F27"/>
     <mergeCell ref="A30:C30"/>
     <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A35:F35"/>
     <mergeCell ref="A29:C29"/>
   </mergeCells>
   <dataValidations count="1">

--- a/templates/23-kano-analysis.xlsx
+++ b/templates/23-kano-analysis.xlsx
@@ -360,9 +360,9 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>6</col>
+      <col>7</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>2</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5400000" cy="2700000"/>
@@ -1237,6 +1237,7 @@
       </c>
       <c r="F25" s="9" t="n"/>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
@@ -1315,6 +1316,7 @@
         <v/>
       </c>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>

--- a/templates/23-kano-analysis.xlsx
+++ b/templates/23-kano-analysis.xlsx
@@ -108,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -124,10 +124,16 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -899,419 +905,457 @@
         <f>IF(D7="","",IF(D7="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D7="Performance","Invest — more is better, and measurable",IF(D7="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D7="Reverse","Stop doing it — they want the opposite",IF(D7="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
-      <c r="F7" s="7" t="n"/>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>Every reopen is one of these. This is the project.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Answered within the time you promised</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Expect it</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Dislike</t>
         </is>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="11">
         <f>IF(OR(B8="",C8=""),"",IF(B8="Like",IF(C8="Like","Questionable",IF(C8="Dislike","Performance","Delighter")),IF(B8="Dislike",IF(C8="Dislike","Questionable","Reverse"),IF(C8="Dislike","Must-have",IF(C8="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="11">
         <f>IF(D8="","",IF(D8="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D8="Performance","Invest — more is better, and measurable",IF(D8="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D8="Reverse","Stop doing it — they want the opposite",IF(D8="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
-      <c r="F8" s="9" t="n"/>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>Our 14.2% reopen rate breaks this one; fixing it earns no praise, only the absence of complaints.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Agent already knows my account history</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>Like</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>Dislike</t>
         </is>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="11">
         <f>IF(OR(B9="",C9=""),"",IF(B9="Like",IF(C9="Like","Questionable",IF(C9="Dislike","Performance","Delighter")),IF(B9="Dislike",IF(C9="Dislike","Questionable","Reverse"),IF(C9="Dislike","Must-have",IF(C9="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="11">
         <f>IF(D9="","",IF(D9="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D9="Performance","Invest — more is better, and measurable",IF(D9="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D9="Reverse","Stop doing it — they want the opposite",IF(D9="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
-      <c r="F9" s="9" t="n"/>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>Worth building: agents currently re-read the case history on every contact.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>Fewer transfers between teams</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Like</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>Dislike</t>
         </is>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="11">
         <f>IF(OR(B10="",C10=""),"",IF(B10="Like",IF(C10="Like","Questionable",IF(C10="Dislike","Performance","Delighter")),IF(B10="Dislike",IF(C10="Dislike","Questionable","Reverse"),IF(C10="Dislike","Must-have",IF(C10="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="11">
         <f>IF(D10="","",IF(D10="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D10="Performance","Invest — more is better, and measurable",IF(D10="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D10="Reverse","Stop doing it — they want the opposite",IF(D10="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
-      <c r="F10" s="9" t="n"/>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>Two transfers a case today. Directly measurable, and it scales.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Proactive notice before I notice the problem</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>Like</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>Live with it</t>
         </is>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="11">
         <f>IF(OR(B11="",C11=""),"",IF(B11="Like",IF(C11="Like","Questionable",IF(C11="Dislike","Performance","Delighter")),IF(B11="Dislike",IF(C11="Dislike","Questionable","Reverse"),IF(C11="Dislike","Must-have",IF(C11="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="11">
         <f>IF(D11="","",IF(D11="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D11="Performance","Invest — more is better, and measurable",IF(D11="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D11="Reverse","Stop doing it — they want the opposite",IF(D11="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
-      <c r="F11" s="9" t="n"/>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>Cheap to add on the back of the posting-confirmation fix — send the note when the batch confirms.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>A follow-up note a week later</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Like</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="11">
         <f>IF(OR(B12="",C12=""),"",IF(B12="Like",IF(C12="Like","Questionable",IF(C12="Dislike","Performance","Delighter")),IF(B12="Dislike",IF(C12="Dislike","Questionable","Reverse"),IF(C12="Dislike","Must-have",IF(C12="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
-      <c r="E12" s="10">
+      <c r="E12" s="11">
         <f>IF(D12="","",IF(D12="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D12="Performance","Invest — more is better, and measurable",IF(D12="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D12="Reverse","Stop doing it — they want the opposite",IF(D12="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
-      <c r="F12" s="9" t="n"/>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>Nice, not urgent. Park it until the must-haves hold.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>Choice of chat colour scheme</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="11">
         <f>IF(OR(B13="",C13=""),"",IF(B13="Like",IF(C13="Like","Questionable",IF(C13="Dislike","Performance","Delighter")),IF(B13="Dislike",IF(C13="Dislike","Questionable","Reverse"),IF(C13="Dislike","Must-have",IF(C13="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
-      <c r="E13" s="10">
+      <c r="E13" s="11">
         <f>IF(D13="","",IF(D13="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D13="Performance","Invest — more is better, and measurable",IF(D13="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D13="Reverse","Stop doing it — they want the opposite",IF(D13="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
-      <c r="F13" s="9" t="n"/>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>Do not spend a day on this.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>A survey after every single contact</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>Dislike</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="11">
         <f>IF(OR(B14="",C14=""),"",IF(B14="Like",IF(C14="Like","Questionable",IF(C14="Dislike","Performance","Delighter")),IF(B14="Dislike",IF(C14="Dislike","Questionable","Reverse"),IF(C14="Dislike","Must-have",IF(C14="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="11">
         <f>IF(D14="","",IF(D14="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D14="Performance","Invest — more is better, and measurable",IF(D14="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D14="Reverse","Stop doing it — they want the opposite",IF(D14="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
-      <c r="F14" s="9" t="n"/>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>Actively harmful — survey fatigue is why our response rate is 17%.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="n"/>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="10">
+      <c r="A15" s="10" t="n"/>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="11">
         <f>IF(OR(B15="",C15=""),"",IF(B15="Like",IF(C15="Like","Questionable",IF(C15="Dislike","Performance","Delighter")),IF(B15="Dislike",IF(C15="Dislike","Questionable","Reverse"),IF(C15="Dislike","Must-have",IF(C15="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
-      <c r="E15" s="10">
+      <c r="E15" s="11">
         <f>IF(D15="","",IF(D15="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D15="Performance","Invest — more is better, and measurable",IF(D15="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D15="Reverse","Stop doing it — they want the opposite",IF(D15="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
-      <c r="F15" s="9" t="n"/>
+      <c r="F15" s="10" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="n"/>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="10">
+      <c r="A16" s="10" t="n"/>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="10" t="n"/>
+      <c r="D16" s="11">
         <f>IF(OR(B16="",C16=""),"",IF(B16="Like",IF(C16="Like","Questionable",IF(C16="Dislike","Performance","Delighter")),IF(B16="Dislike",IF(C16="Dislike","Questionable","Reverse"),IF(C16="Dislike","Must-have",IF(C16="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
-      <c r="E16" s="10">
+      <c r="E16" s="11">
         <f>IF(D16="","",IF(D16="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D16="Performance","Invest — more is better, and measurable",IF(D16="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D16="Reverse","Stop doing it — they want the opposite",IF(D16="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
-      <c r="F16" s="9" t="n"/>
+      <c r="F16" s="10" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="n"/>
-      <c r="B17" s="9" t="n"/>
-      <c r="C17" s="9" t="n"/>
-      <c r="D17" s="10">
+      <c r="A17" s="10" t="n"/>
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="11">
         <f>IF(OR(B17="",C17=""),"",IF(B17="Like",IF(C17="Like","Questionable",IF(C17="Dislike","Performance","Delighter")),IF(B17="Dislike",IF(C17="Dislike","Questionable","Reverse"),IF(C17="Dislike","Must-have",IF(C17="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
-      <c r="E17" s="10">
+      <c r="E17" s="11">
         <f>IF(D17="","",IF(D17="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D17="Performance","Invest — more is better, and measurable",IF(D17="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D17="Reverse","Stop doing it — they want the opposite",IF(D17="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
-      <c r="F17" s="9" t="n"/>
+      <c r="F17" s="10" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="n"/>
-      <c r="B18" s="9" t="n"/>
-      <c r="C18" s="9" t="n"/>
-      <c r="D18" s="10">
+      <c r="A18" s="10" t="n"/>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="11">
         <f>IF(OR(B18="",C18=""),"",IF(B18="Like",IF(C18="Like","Questionable",IF(C18="Dislike","Performance","Delighter")),IF(B18="Dislike",IF(C18="Dislike","Questionable","Reverse"),IF(C18="Dislike","Must-have",IF(C18="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
-      <c r="E18" s="10">
+      <c r="E18" s="11">
         <f>IF(D18="","",IF(D18="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D18="Performance","Invest — more is better, and measurable",IF(D18="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D18="Reverse","Stop doing it — they want the opposite",IF(D18="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
-      <c r="F18" s="9" t="n"/>
+      <c r="F18" s="10" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="n"/>
-      <c r="B19" s="9" t="n"/>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="10">
+      <c r="A19" s="10" t="n"/>
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="11">
         <f>IF(OR(B19="",C19=""),"",IF(B19="Like",IF(C19="Like","Questionable",IF(C19="Dislike","Performance","Delighter")),IF(B19="Dislike",IF(C19="Dislike","Questionable","Reverse"),IF(C19="Dislike","Must-have",IF(C19="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
-      <c r="E19" s="10">
+      <c r="E19" s="11">
         <f>IF(D19="","",IF(D19="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D19="Performance","Invest — more is better, and measurable",IF(D19="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D19="Reverse","Stop doing it — they want the opposite",IF(D19="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
-      <c r="F19" s="9" t="n"/>
+      <c r="F19" s="10" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="n"/>
-      <c r="B20" s="9" t="n"/>
-      <c r="C20" s="9" t="n"/>
-      <c r="D20" s="10">
+      <c r="A20" s="10" t="n"/>
+      <c r="B20" s="10" t="n"/>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="11">
         <f>IF(OR(B20="",C20=""),"",IF(B20="Like",IF(C20="Like","Questionable",IF(C20="Dislike","Performance","Delighter")),IF(B20="Dislike",IF(C20="Dislike","Questionable","Reverse"),IF(C20="Dislike","Must-have",IF(C20="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
-      <c r="E20" s="10">
+      <c r="E20" s="11">
         <f>IF(D20="","",IF(D20="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D20="Performance","Invest — more is better, and measurable",IF(D20="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D20="Reverse","Stop doing it — they want the opposite",IF(D20="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
-      <c r="F20" s="9" t="n"/>
+      <c r="F20" s="10" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="n"/>
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="9" t="n"/>
-      <c r="D21" s="10">
+      <c r="A21" s="10" t="n"/>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="11">
         <f>IF(OR(B21="",C21=""),"",IF(B21="Like",IF(C21="Like","Questionable",IF(C21="Dislike","Performance","Delighter")),IF(B21="Dislike",IF(C21="Dislike","Questionable","Reverse"),IF(C21="Dislike","Must-have",IF(C21="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
-      <c r="E21" s="10">
+      <c r="E21" s="11">
         <f>IF(D21="","",IF(D21="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D21="Performance","Invest — more is better, and measurable",IF(D21="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D21="Reverse","Stop doing it — they want the opposite",IF(D21="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
-      <c r="F21" s="9" t="n"/>
+      <c r="F21" s="10" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="n"/>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="10">
+      <c r="A22" s="10" t="n"/>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="11">
         <f>IF(OR(B22="",C22=""),"",IF(B22="Like",IF(C22="Like","Questionable",IF(C22="Dislike","Performance","Delighter")),IF(B22="Dislike",IF(C22="Dislike","Questionable","Reverse"),IF(C22="Dislike","Must-have",IF(C22="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
-      <c r="E22" s="10">
+      <c r="E22" s="11">
         <f>IF(D22="","",IF(D22="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D22="Performance","Invest — more is better, and measurable",IF(D22="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D22="Reverse","Stop doing it — they want the opposite",IF(D22="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
-      <c r="F22" s="9" t="n"/>
+      <c r="F22" s="10" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="n"/>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="9" t="n"/>
-      <c r="D23" s="10">
+      <c r="A23" s="10" t="n"/>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="11">
         <f>IF(OR(B23="",C23=""),"",IF(B23="Like",IF(C23="Like","Questionable",IF(C23="Dislike","Performance","Delighter")),IF(B23="Dislike",IF(C23="Dislike","Questionable","Reverse"),IF(C23="Dislike","Must-have",IF(C23="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
-      <c r="E23" s="10">
+      <c r="E23" s="11">
         <f>IF(D23="","",IF(D23="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D23="Performance","Invest — more is better, and measurable",IF(D23="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D23="Reverse","Stop doing it — they want the opposite",IF(D23="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
-      <c r="F23" s="9" t="n"/>
+      <c r="F23" s="10" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="n"/>
-      <c r="B24" s="9" t="n"/>
-      <c r="C24" s="9" t="n"/>
-      <c r="D24" s="10">
+      <c r="A24" s="10" t="n"/>
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="10" t="n"/>
+      <c r="D24" s="11">
         <f>IF(OR(B24="",C24=""),"",IF(B24="Like",IF(C24="Like","Questionable",IF(C24="Dislike","Performance","Delighter")),IF(B24="Dislike",IF(C24="Dislike","Questionable","Reverse"),IF(C24="Dislike","Must-have",IF(C24="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
-      <c r="E24" s="10">
+      <c r="E24" s="11">
         <f>IF(D24="","",IF(D24="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D24="Performance","Invest — more is better, and measurable",IF(D24="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D24="Reverse","Stop doing it — they want the opposite",IF(D24="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
-      <c r="F24" s="9" t="n"/>
+      <c r="F24" s="10" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="n"/>
-      <c r="B25" s="9" t="n"/>
-      <c r="C25" s="9" t="n"/>
-      <c r="D25" s="10">
+      <c r="A25" s="10" t="n"/>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="11">
         <f>IF(OR(B25="",C25=""),"",IF(B25="Like",IF(C25="Like","Questionable",IF(C25="Dislike","Performance","Delighter")),IF(B25="Dislike",IF(C25="Dislike","Questionable","Reverse"),IF(C25="Dislike","Must-have",IF(C25="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
-      <c r="E25" s="10">
+      <c r="E25" s="11">
         <f>IF(D25="","",IF(D25="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D25="Performance","Invest — more is better, and measurable",IF(D25="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D25="Reverse","Stop doing it — they want the opposite",IF(D25="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
-      <c r="F25" s="9" t="n"/>
-    </row>
-    <row r="26"/>
+      <c r="F25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="75" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>How to fill the last column. The category is arithmetic; this column is the decision, and it is the only part of the sheet a sponsor will read. Write what the category means for THIS operation — name the metric it moves, or say plainly that it is not worth spending on. A Must-have you already meet needs one line saying so; a Must-have you fail is your project. Rows 7 to 14 are worked examples: delete them and write your own.</t>
+        </is>
+      </c>
+    </row>
     <row r="27">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>WHERE YOUR EFFORT SHOULD GO</t>
         </is>
       </c>
-      <c r="B27" s="12" t="n"/>
-      <c r="C27" s="12" t="n"/>
-      <c r="D27" s="12" t="n"/>
-      <c r="E27" s="12" t="n"/>
-      <c r="F27" s="12" t="n"/>
+      <c r="B27" s="14" t="n"/>
+      <c r="C27" s="14" t="n"/>
+      <c r="D27" s="14" t="n"/>
+      <c r="E27" s="14" t="n"/>
+      <c r="F27" s="14" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>Must-haves — table stakes</t>
         </is>
       </c>
-      <c r="D28" s="10">
+      <c r="D28" s="11">
         <f>COUNTIF($D$7:$D$25,"Must-have")</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="13" t="inlineStr">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>Performance — scale with investment</t>
         </is>
       </c>
-      <c r="D29" s="10">
+      <c r="D29" s="11">
         <f>COUNTIF($D$7:$D$25,"Performance")</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="13" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>Delighters — differentiators</t>
         </is>
       </c>
-      <c r="D30" s="10">
+      <c r="D30" s="11">
         <f>COUNTIF($D$7:$D$25,"Delighter")</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="inlineStr">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t>Indifferent — stop spending here</t>
         </is>
       </c>
-      <c r="D31" s="10">
+      <c r="D31" s="11">
         <f>COUNTIF($D$7:$D$25,"Indifferent")</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="13" t="inlineStr">
+      <c r="A32" s="15" t="inlineStr">
         <is>
           <t>Reverse — you are actively annoying people</t>
         </is>
       </c>
-      <c r="D32" s="10">
+      <c r="D32" s="11">
         <f>COUNTIF($D$7:$D$25,"Reverse")</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="13" t="inlineStr">
+      <c r="A33" s="15" t="inlineStr">
         <is>
           <t>Questionable — the answers contradict; re-ask</t>
         </is>
       </c>
-      <c r="D33" s="10">
+      <c r="D33" s="11">
         <f>COUNTIF($D$7:$D$25,"Questionable")</f>
         <v/>
       </c>
@@ -1325,9 +1369,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
+    <mergeCell ref="A2:F2"/>
     <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A2:F2"/>
     <mergeCell ref="A33:C33"/>
     <mergeCell ref="A32:C32"/>
     <mergeCell ref="A1:F1"/>
@@ -1336,6 +1380,7 @@
     <mergeCell ref="A30:C30"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A29:C29"/>
   </mergeCells>
   <dataValidations count="1">

--- a/templates/23-kano-analysis.xlsx
+++ b/templates/23-kano-analysis.xlsx
@@ -912,210 +912,210 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Answered within the time you promised</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Expect it</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>Dislike</t>
         </is>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="8">
         <f>IF(OR(B8="",C8=""),"",IF(B8="Like",IF(C8="Like","Questionable",IF(C8="Dislike","Performance","Delighter")),IF(B8="Dislike",IF(C8="Dislike","Questionable","Reverse"),IF(C8="Dislike","Must-have",IF(C8="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="8">
         <f>IF(D8="","",IF(D8="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D8="Performance","Invest — more is better, and measurable",IF(D8="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D8="Reverse","Stop doing it — they want the opposite",IF(D8="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="9" t="inlineStr">
         <is>
           <t>Our 14.2% reopen rate breaks this one; fixing it earns no praise, only the absence of complaints.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Agent already knows my account history</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Like</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>Dislike</t>
         </is>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="8">
         <f>IF(OR(B9="",C9=""),"",IF(B9="Like",IF(C9="Like","Questionable",IF(C9="Dislike","Performance","Delighter")),IF(B9="Dislike",IF(C9="Dislike","Questionable","Reverse"),IF(C9="Dislike","Must-have",IF(C9="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="8">
         <f>IF(D9="","",IF(D9="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D9="Performance","Invest — more is better, and measurable",IF(D9="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D9="Reverse","Stop doing it — they want the opposite",IF(D9="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>Worth building: agents currently re-read the case history on every contact.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Fewer transfers between teams</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Like</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>Dislike</t>
         </is>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="8">
         <f>IF(OR(B10="",C10=""),"",IF(B10="Like",IF(C10="Like","Questionable",IF(C10="Dislike","Performance","Delighter")),IF(B10="Dislike",IF(C10="Dislike","Questionable","Reverse"),IF(C10="Dislike","Must-have",IF(C10="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="8">
         <f>IF(D10="","",IF(D10="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D10="Performance","Invest — more is better, and measurable",IF(D10="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D10="Reverse","Stop doing it — they want the opposite",IF(D10="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="9" t="inlineStr">
         <is>
           <t>Two transfers a case today. Directly measurable, and it scales.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Proactive notice before I notice the problem</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Like</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>Live with it</t>
         </is>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="8">
         <f>IF(OR(B11="",C11=""),"",IF(B11="Like",IF(C11="Like","Questionable",IF(C11="Dislike","Performance","Delighter")),IF(B11="Dislike",IF(C11="Dislike","Questionable","Reverse"),IF(C11="Dislike","Must-have",IF(C11="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="8">
         <f>IF(D11="","",IF(D11="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D11="Performance","Invest — more is better, and measurable",IF(D11="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D11="Reverse","Stop doing it — they want the opposite",IF(D11="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>Cheap to add on the back of the posting-confirmation fix — send the note when the batch confirms.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>A follow-up note a week later</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Like</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="8">
         <f>IF(OR(B12="",C12=""),"",IF(B12="Like",IF(C12="Like","Questionable",IF(C12="Dislike","Performance","Delighter")),IF(B12="Dislike",IF(C12="Dislike","Questionable","Reverse"),IF(C12="Dislike","Must-have",IF(C12="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="8">
         <f>IF(D12="","",IF(D12="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D12="Performance","Invest — more is better, and measurable",IF(D12="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D12="Reverse","Stop doing it — they want the opposite",IF(D12="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="9" t="inlineStr">
         <is>
           <t>Nice, not urgent. Park it until the must-haves hold.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Choice of chat colour scheme</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="8">
         <f>IF(OR(B13="",C13=""),"",IF(B13="Like",IF(C13="Like","Questionable",IF(C13="Dislike","Performance","Delighter")),IF(B13="Dislike",IF(C13="Dislike","Questionable","Reverse"),IF(C13="Dislike","Must-have",IF(C13="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="8">
         <f>IF(D13="","",IF(D13="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D13="Performance","Invest — more is better, and measurable",IF(D13="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D13="Reverse","Stop doing it — they want the opposite",IF(D13="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>Do not spend a day on this.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>A survey after every single contact</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Dislike</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="8">
         <f>IF(OR(B14="",C14=""),"",IF(B14="Like",IF(C14="Like","Questionable",IF(C14="Dislike","Performance","Delighter")),IF(B14="Dislike",IF(C14="Dislike","Questionable","Reverse"),IF(C14="Dislike","Must-have",IF(C14="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="8">
         <f>IF(D14="","",IF(D14="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D14="Performance","Invest — more is better, and measurable",IF(D14="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D14="Reverse","Stop doing it — they want the opposite",IF(D14="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="F14" s="9" t="inlineStr">
         <is>
           <t>Actively harmful — survey fatigue is why our response rate is 17%.</t>
         </is>

--- a/templates/23-kano-analysis.xlsx
+++ b/templates/23-kano-analysis.xlsx
@@ -717,14 +717,14 @@
     <row r="6">
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>Green row</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
+          <t>Green cells</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>A worked example so you can see the expected format. Delete it when you start.</t>
+          <t>A worked example, so you can see the expected format and the charts say something the moment you open the file. Replace it with your own data when you start.</t>
         </is>
       </c>
     </row>

--- a/templates/23-kano-analysis.xlsx
+++ b/templates/23-kano-analysis.xlsx
@@ -108,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -123,14 +123,13 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1125,11 +1124,11 @@
       <c r="A15" s="10" t="n"/>
       <c r="B15" s="10" t="n"/>
       <c r="C15" s="10" t="n"/>
-      <c r="D15" s="11">
+      <c r="D15" s="8">
         <f>IF(OR(B15="",C15=""),"",IF(B15="Like",IF(C15="Like","Questionable",IF(C15="Dislike","Performance","Delighter")),IF(B15="Dislike",IF(C15="Dislike","Questionable","Reverse"),IF(C15="Dislike","Must-have",IF(C15="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
-      <c r="E15" s="11">
+      <c r="E15" s="8">
         <f>IF(D15="","",IF(D15="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D15="Performance","Invest — more is better, and measurable",IF(D15="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D15="Reverse","Stop doing it — they want the opposite",IF(D15="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
@@ -1139,11 +1138,11 @@
       <c r="A16" s="10" t="n"/>
       <c r="B16" s="10" t="n"/>
       <c r="C16" s="10" t="n"/>
-      <c r="D16" s="11">
+      <c r="D16" s="8">
         <f>IF(OR(B16="",C16=""),"",IF(B16="Like",IF(C16="Like","Questionable",IF(C16="Dislike","Performance","Delighter")),IF(B16="Dislike",IF(C16="Dislike","Questionable","Reverse"),IF(C16="Dislike","Must-have",IF(C16="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
-      <c r="E16" s="11">
+      <c r="E16" s="8">
         <f>IF(D16="","",IF(D16="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D16="Performance","Invest — more is better, and measurable",IF(D16="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D16="Reverse","Stop doing it — they want the opposite",IF(D16="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
@@ -1153,11 +1152,11 @@
       <c r="A17" s="10" t="n"/>
       <c r="B17" s="10" t="n"/>
       <c r="C17" s="10" t="n"/>
-      <c r="D17" s="11">
+      <c r="D17" s="8">
         <f>IF(OR(B17="",C17=""),"",IF(B17="Like",IF(C17="Like","Questionable",IF(C17="Dislike","Performance","Delighter")),IF(B17="Dislike",IF(C17="Dislike","Questionable","Reverse"),IF(C17="Dislike","Must-have",IF(C17="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
-      <c r="E17" s="11">
+      <c r="E17" s="8">
         <f>IF(D17="","",IF(D17="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D17="Performance","Invest — more is better, and measurable",IF(D17="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D17="Reverse","Stop doing it — they want the opposite",IF(D17="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
@@ -1167,11 +1166,11 @@
       <c r="A18" s="10" t="n"/>
       <c r="B18" s="10" t="n"/>
       <c r="C18" s="10" t="n"/>
-      <c r="D18" s="11">
+      <c r="D18" s="8">
         <f>IF(OR(B18="",C18=""),"",IF(B18="Like",IF(C18="Like","Questionable",IF(C18="Dislike","Performance","Delighter")),IF(B18="Dislike",IF(C18="Dislike","Questionable","Reverse"),IF(C18="Dislike","Must-have",IF(C18="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="8">
         <f>IF(D18="","",IF(D18="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D18="Performance","Invest — more is better, and measurable",IF(D18="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D18="Reverse","Stop doing it — they want the opposite",IF(D18="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
@@ -1181,11 +1180,11 @@
       <c r="A19" s="10" t="n"/>
       <c r="B19" s="10" t="n"/>
       <c r="C19" s="10" t="n"/>
-      <c r="D19" s="11">
+      <c r="D19" s="8">
         <f>IF(OR(B19="",C19=""),"",IF(B19="Like",IF(C19="Like","Questionable",IF(C19="Dislike","Performance","Delighter")),IF(B19="Dislike",IF(C19="Dislike","Questionable","Reverse"),IF(C19="Dislike","Must-have",IF(C19="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
-      <c r="E19" s="11">
+      <c r="E19" s="8">
         <f>IF(D19="","",IF(D19="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D19="Performance","Invest — more is better, and measurable",IF(D19="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D19="Reverse","Stop doing it — they want the opposite",IF(D19="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
@@ -1195,11 +1194,11 @@
       <c r="A20" s="10" t="n"/>
       <c r="B20" s="10" t="n"/>
       <c r="C20" s="10" t="n"/>
-      <c r="D20" s="11">
+      <c r="D20" s="8">
         <f>IF(OR(B20="",C20=""),"",IF(B20="Like",IF(C20="Like","Questionable",IF(C20="Dislike","Performance","Delighter")),IF(B20="Dislike",IF(C20="Dislike","Questionable","Reverse"),IF(C20="Dislike","Must-have",IF(C20="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
-      <c r="E20" s="11">
+      <c r="E20" s="8">
         <f>IF(D20="","",IF(D20="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D20="Performance","Invest — more is better, and measurable",IF(D20="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D20="Reverse","Stop doing it — they want the opposite",IF(D20="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
@@ -1209,11 +1208,11 @@
       <c r="A21" s="10" t="n"/>
       <c r="B21" s="10" t="n"/>
       <c r="C21" s="10" t="n"/>
-      <c r="D21" s="11">
+      <c r="D21" s="8">
         <f>IF(OR(B21="",C21=""),"",IF(B21="Like",IF(C21="Like","Questionable",IF(C21="Dislike","Performance","Delighter")),IF(B21="Dislike",IF(C21="Dislike","Questionable","Reverse"),IF(C21="Dislike","Must-have",IF(C21="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
-      <c r="E21" s="11">
+      <c r="E21" s="8">
         <f>IF(D21="","",IF(D21="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D21="Performance","Invest — more is better, and measurable",IF(D21="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D21="Reverse","Stop doing it — they want the opposite",IF(D21="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
@@ -1223,11 +1222,11 @@
       <c r="A22" s="10" t="n"/>
       <c r="B22" s="10" t="n"/>
       <c r="C22" s="10" t="n"/>
-      <c r="D22" s="11">
+      <c r="D22" s="8">
         <f>IF(OR(B22="",C22=""),"",IF(B22="Like",IF(C22="Like","Questionable",IF(C22="Dislike","Performance","Delighter")),IF(B22="Dislike",IF(C22="Dislike","Questionable","Reverse"),IF(C22="Dislike","Must-have",IF(C22="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
-      <c r="E22" s="11">
+      <c r="E22" s="8">
         <f>IF(D22="","",IF(D22="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D22="Performance","Invest — more is better, and measurable",IF(D22="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D22="Reverse","Stop doing it — they want the opposite",IF(D22="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
@@ -1237,11 +1236,11 @@
       <c r="A23" s="10" t="n"/>
       <c r="B23" s="10" t="n"/>
       <c r="C23" s="10" t="n"/>
-      <c r="D23" s="11">
+      <c r="D23" s="8">
         <f>IF(OR(B23="",C23=""),"",IF(B23="Like",IF(C23="Like","Questionable",IF(C23="Dislike","Performance","Delighter")),IF(B23="Dislike",IF(C23="Dislike","Questionable","Reverse"),IF(C23="Dislike","Must-have",IF(C23="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
-      <c r="E23" s="11">
+      <c r="E23" s="8">
         <f>IF(D23="","",IF(D23="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D23="Performance","Invest — more is better, and measurable",IF(D23="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D23="Reverse","Stop doing it — they want the opposite",IF(D23="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
@@ -1251,11 +1250,11 @@
       <c r="A24" s="10" t="n"/>
       <c r="B24" s="10" t="n"/>
       <c r="C24" s="10" t="n"/>
-      <c r="D24" s="11">
+      <c r="D24" s="8">
         <f>IF(OR(B24="",C24=""),"",IF(B24="Like",IF(C24="Like","Questionable",IF(C24="Dislike","Performance","Delighter")),IF(B24="Dislike",IF(C24="Dislike","Questionable","Reverse"),IF(C24="Dislike","Must-have",IF(C24="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
-      <c r="E24" s="11">
+      <c r="E24" s="8">
         <f>IF(D24="","",IF(D24="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D24="Performance","Invest — more is better, and measurable",IF(D24="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D24="Reverse","Stop doing it — they want the opposite",IF(D24="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
@@ -1265,97 +1264,97 @@
       <c r="A25" s="10" t="n"/>
       <c r="B25" s="10" t="n"/>
       <c r="C25" s="10" t="n"/>
-      <c r="D25" s="11">
+      <c r="D25" s="8">
         <f>IF(OR(B25="",C25=""),"",IF(B25="Like",IF(C25="Like","Questionable",IF(C25="Dislike","Performance","Delighter")),IF(B25="Dislike",IF(C25="Dislike","Questionable","Reverse"),IF(C25="Dislike","Must-have",IF(C25="Like","Reverse","Indifferent")))))</f>
         <v/>
       </c>
-      <c r="E25" s="11">
+      <c r="E25" s="8">
         <f>IF(D25="","",IF(D25="Must-have","Fix it — no credit for doing it, all the blame for not",IF(D25="Performance","Invest — more is better, and measurable",IF(D25="Delighter","Consider — wins goodwill, costs you nothing if absent",IF(D25="Reverse","Stop doing it — they want the opposite",IF(D25="Questionable","Re-ask — the two answers contradict each other","Do not spend here"))))))</f>
         <v/>
       </c>
       <c r="F25" s="10" t="n"/>
     </row>
     <row r="26" ht="75" customHeight="1">
-      <c r="A26" s="12" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>How to fill the last column. The category is arithmetic; this column is the decision, and it is the only part of the sheet a sponsor will read. Write what the category means for THIS operation — name the metric it moves, or say plainly that it is not worth spending on. A Must-have you already meet needs one line saying so; a Must-have you fail is your project. Rows 7 to 14 are worked examples: delete them and write your own.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>WHERE YOUR EFFORT SHOULD GO</t>
         </is>
       </c>
-      <c r="B27" s="14" t="n"/>
-      <c r="C27" s="14" t="n"/>
-      <c r="D27" s="14" t="n"/>
-      <c r="E27" s="14" t="n"/>
-      <c r="F27" s="14" t="n"/>
+      <c r="B27" s="13" t="n"/>
+      <c r="C27" s="13" t="n"/>
+      <c r="D27" s="13" t="n"/>
+      <c r="E27" s="13" t="n"/>
+      <c r="F27" s="13" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="14" t="inlineStr">
         <is>
           <t>Must-haves — table stakes</t>
         </is>
       </c>
-      <c r="D28" s="11">
+      <c r="D28" s="8">
         <f>COUNTIF($D$7:$D$25,"Must-have")</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="14" t="inlineStr">
         <is>
           <t>Performance — scale with investment</t>
         </is>
       </c>
-      <c r="D29" s="11">
+      <c r="D29" s="8">
         <f>COUNTIF($D$7:$D$25,"Performance")</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="A30" s="14" t="inlineStr">
         <is>
           <t>Delighters — differentiators</t>
         </is>
       </c>
-      <c r="D30" s="11">
+      <c r="D30" s="8">
         <f>COUNTIF($D$7:$D$25,"Delighter")</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="A31" s="14" t="inlineStr">
         <is>
           <t>Indifferent — stop spending here</t>
         </is>
       </c>
-      <c r="D31" s="11">
+      <c r="D31" s="8">
         <f>COUNTIF($D$7:$D$25,"Indifferent")</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="A32" s="14" t="inlineStr">
         <is>
           <t>Reverse — you are actively annoying people</t>
         </is>
       </c>
-      <c r="D32" s="11">
+      <c r="D32" s="8">
         <f>COUNTIF($D$7:$D$25,"Reverse")</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="A33" s="14" t="inlineStr">
         <is>
           <t>Questionable — the answers contradict; re-ask</t>
         </is>
       </c>
-      <c r="D33" s="11">
+      <c r="D33" s="8">
         <f>COUNTIF($D$7:$D$25,"Questionable")</f>
         <v/>
       </c>

--- a/templates/23-kano-analysis.xlsx
+++ b/templates/23-kano-analysis.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,6 +51,11 @@
     </font>
     <font>
       <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF4B5563"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="8">
@@ -108,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -128,6 +133,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -365,7 +373,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>7</col>
+      <col>8</col>
       <colOff>0</colOff>
       <row>2</row>
       <rowOff>0</rowOff>
@@ -809,7 +817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:O35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -818,6 +826,15 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1246,7 +1263,7 @@
       </c>
       <c r="F23" s="10" t="n"/>
     </row>
-    <row r="24">
+    <row r="24" ht="66" customHeight="1">
       <c r="A24" s="10" t="n"/>
       <c r="B24" s="10" t="n"/>
       <c r="C24" s="10" t="n"/>
@@ -1259,6 +1276,12 @@
         <v/>
       </c>
       <c r="F24" s="10" t="n"/>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
+          <t>HOW TO READ IT.  Delighters earn a premium today and become expected within a year or two, so read this as a snapshot with a shelf life. What should worry you is a feature you are proud of sitting in Indifferent: it costs to build and nobody values it.
+SO:  Build the Must-bes to parity and spend the remaining effort on one Delighter. Anything in Indifferent comes out of the scope now, while removing it is still cheap.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="n"/>
@@ -1275,26 +1298,26 @@
       <c r="F25" s="10" t="n"/>
     </row>
     <row r="26" ht="75" customHeight="1">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>How to fill the last column. The category is arithmetic; this column is the decision, and it is the only part of the sheet a sponsor will read. Write what the category means for THIS operation — name the metric it moves, or say plainly that it is not worth spending on. A Must-have you already meet needs one line saying so; a Must-have you fail is your project. Rows 7 to 14 are worked examples: delete them and write your own.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>WHERE YOUR EFFORT SHOULD GO</t>
         </is>
       </c>
-      <c r="B27" s="13" t="n"/>
-      <c r="C27" s="13" t="n"/>
-      <c r="D27" s="13" t="n"/>
-      <c r="E27" s="13" t="n"/>
-      <c r="F27" s="13" t="n"/>
+      <c r="B27" s="14" t="n"/>
+      <c r="C27" s="14" t="n"/>
+      <c r="D27" s="14" t="n"/>
+      <c r="E27" s="14" t="n"/>
+      <c r="F27" s="14" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="14" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>Must-haves — table stakes</t>
         </is>
@@ -1305,7 +1328,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="14" t="inlineStr">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>Performance — scale with investment</t>
         </is>
@@ -1316,7 +1339,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="14" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>Delighters — differentiators</t>
         </is>
@@ -1327,7 +1350,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="14" t="inlineStr">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t>Indifferent — stop spending here</t>
         </is>
@@ -1338,7 +1361,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="14" t="inlineStr">
+      <c r="A32" s="15" t="inlineStr">
         <is>
           <t>Reverse — you are actively annoying people</t>
         </is>
@@ -1349,7 +1372,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="14" t="inlineStr">
+      <c r="A33" s="15" t="inlineStr">
         <is>
           <t>Questionable — the answers contradict; re-ask</t>
         </is>
@@ -1368,9 +1391,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A28:C28"/>
+    <mergeCell ref="G24:O24"/>
     <mergeCell ref="A33:C33"/>
     <mergeCell ref="A32:C32"/>
     <mergeCell ref="A1:F1"/>
